--- a/Experiments/outputs/scenario_2.xlsx
+++ b/Experiments/outputs/scenario_2.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1279.324444755459</v>
+        <v>1199.64094015407</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4465510845184326</v>
+        <v>1.179387331008911</v>
       </c>
       <c r="E2" t="n">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="F2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G2" t="n">
+        <v>127</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2374.838483289966</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16.70650196075439</v>
+      </c>
+      <c r="J2" t="n">
+        <v>419</v>
+      </c>
+      <c r="K2" t="n">
         <v>66</v>
       </c>
-      <c r="G2" t="n">
-        <v>111</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2590.853853481291</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.934998989105225</v>
-      </c>
-      <c r="J2" t="n">
-        <v>449</v>
-      </c>
-      <c r="K2" t="n">
-        <v>74</v>
-      </c>
       <c r="L2" t="n">
-        <v>522</v>
+        <v>582</v>
       </c>
       <c r="M2" t="n">
-        <v>6815.883470731718</v>
+        <v>6589.502176721426</v>
       </c>
       <c r="N2" t="n">
-        <v>4.877985715866089</v>
+        <v>6.003299951553345</v>
       </c>
       <c r="O2" t="n">
-        <v>1848</v>
+        <v>2099</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5929</v>
+        <v>6737</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8123024769644254</v>
+        <v>0.8179466509030057</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6198799664626381</v>
+        <v>0.6396027469754088</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1145.919409247479</v>
+        <v>1256.998242386261</v>
       </c>
       <c r="D3" t="n">
-        <v>0.462385892868042</v>
+        <v>1.281131982803345</v>
       </c>
       <c r="E3" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H3" t="n">
-        <v>2486.332170192617</v>
+        <v>2408.057524180186</v>
       </c>
       <c r="I3" t="n">
-        <v>1.491813182830811</v>
+        <v>16.80185079574585</v>
       </c>
       <c r="J3" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L3" t="n">
-        <v>497</v>
+        <v>592</v>
       </c>
       <c r="M3" t="n">
-        <v>6759.789402323547</v>
+        <v>6484.916333469898</v>
       </c>
       <c r="N3" t="n">
-        <v>5.343031883239746</v>
+        <v>5.759440898895264</v>
       </c>
       <c r="O3" t="n">
-        <v>1872</v>
+        <v>2104</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>6069</v>
+        <v>6658</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8304800133487011</v>
+        <v>0.8061658504522793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6321879244732109</v>
+        <v>0.6286679117582846</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1163.766417022468</v>
+        <v>1161.521584969251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4356541633605957</v>
+        <v>1.155527353286743</v>
       </c>
       <c r="E4" t="n">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="H4" t="n">
-        <v>2517.596578055638</v>
+        <v>2506.134431378592</v>
       </c>
       <c r="I4" t="n">
-        <v>1.718365907669067</v>
+        <v>15.36139106750488</v>
       </c>
       <c r="J4" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L4" t="n">
-        <v>530</v>
+        <v>643</v>
       </c>
       <c r="M4" t="n">
-        <v>6813.868103181032</v>
+        <v>6477.148929360631</v>
       </c>
       <c r="N4" t="n">
-        <v>4.913983106613159</v>
+        <v>5.68611216545105</v>
       </c>
       <c r="O4" t="n">
-        <v>1904</v>
+        <v>2113</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>6118</v>
+        <v>6762</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8292062013235671</v>
+        <v>0.8206739419400835</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6305187391460797</v>
+        <v>0.6130806225531739</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1266.350606356289</v>
+        <v>1246.263864666228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4674971103668213</v>
+        <v>1.720864057540894</v>
       </c>
       <c r="E5" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H5" t="n">
-        <v>2484.130480324609</v>
+        <v>2417.282322466951</v>
       </c>
       <c r="I5" t="n">
-        <v>1.875243902206421</v>
+        <v>15.7919590473175</v>
       </c>
       <c r="J5" t="n">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="K5" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L5" t="n">
-        <v>492</v>
+        <v>613</v>
       </c>
       <c r="M5" t="n">
-        <v>6727.612905537415</v>
+        <v>6482.345240155623</v>
       </c>
       <c r="N5" t="n">
-        <v>4.334763050079346</v>
+        <v>4.645852088928223</v>
       </c>
       <c r="O5" t="n">
-        <v>1841</v>
+        <v>2070</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>5875</v>
+        <v>6688</v>
       </c>
       <c r="R5" t="n">
-        <v>0.811768211973972</v>
+        <v>0.8077449104459749</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6307560326070556</v>
+        <v>0.6270975653236083</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1280.085771903882</v>
+        <v>1314.537209562098</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6342320442199707</v>
+        <v>1.270658016204834</v>
       </c>
       <c r="E6" t="n">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H6" t="n">
-        <v>2262.936144761205</v>
+        <v>2279.1121586119</v>
       </c>
       <c r="I6" t="n">
-        <v>2.151333808898926</v>
+        <v>11.56591510772705</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L6" t="n">
-        <v>500</v>
+        <v>577</v>
       </c>
       <c r="M6" t="n">
-        <v>6753.870837122067</v>
+        <v>6695.901006580472</v>
       </c>
       <c r="N6" t="n">
-        <v>5.023499965667725</v>
+        <v>5.697988033294678</v>
       </c>
       <c r="O6" t="n">
-        <v>1849</v>
+        <v>2114</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>5835</v>
+        <v>6587</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8104663528849263</v>
+        <v>0.8036803100478604</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6649423420532161</v>
+        <v>0.6596257686049902</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1243.298154029902</v>
+        <v>1165.55564803728</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4524369239807129</v>
+        <v>0.7933650016784668</v>
       </c>
       <c r="E7" t="n">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>2474.812328853149</v>
+        <v>2432.571716696542</v>
       </c>
       <c r="I7" t="n">
-        <v>1.628428936004639</v>
+        <v>12.54544401168823</v>
       </c>
       <c r="J7" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>514</v>
+        <v>620</v>
       </c>
       <c r="M7" t="n">
-        <v>6762.077708086134</v>
+        <v>6512.263046017078</v>
       </c>
       <c r="N7" t="n">
-        <v>4.822170972824097</v>
+        <v>4.569674015045166</v>
       </c>
       <c r="O7" t="n">
-        <v>1914</v>
+        <v>2070</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>5962</v>
+        <v>6590</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8161366657258082</v>
+        <v>0.8210214114815066</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6340159880307568</v>
+        <v>0.6264629208759754</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1252.368021691324</v>
+        <v>1243.67187859209</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5877540111541748</v>
+        <v>1.183265924453735</v>
       </c>
       <c r="E8" t="n">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H8" t="n">
-        <v>2557.500084745298</v>
+        <v>2441.506735285663</v>
       </c>
       <c r="I8" t="n">
-        <v>1.601255178451538</v>
+        <v>12.41290783882141</v>
       </c>
       <c r="J8" t="n">
         <v>450</v>
       </c>
       <c r="K8" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L8" t="n">
-        <v>519</v>
+        <v>615</v>
       </c>
       <c r="M8" t="n">
-        <v>6876.317607719643</v>
+        <v>6461.24583153123</v>
       </c>
       <c r="N8" t="n">
-        <v>5.109121799468994</v>
+        <v>4.95296311378479</v>
       </c>
       <c r="O8" t="n">
-        <v>1873</v>
+        <v>2051</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>5934</v>
+        <v>6502</v>
       </c>
       <c r="R8" t="n">
-        <v>0.817872283809962</v>
+        <v>0.8075182540613292</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6280712685705294</v>
+        <v>0.6221306542198135</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1268.191661185484</v>
+        <v>1160.537761735735</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4975380897521973</v>
+        <v>0.8293061256408691</v>
       </c>
       <c r="E9" t="n">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G9" t="n">
+        <v>105</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2422.009602580113</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.49997591972351</v>
+      </c>
+      <c r="J9" t="n">
+        <v>454</v>
+      </c>
+      <c r="K9" t="n">
         <v>62</v>
       </c>
-      <c r="G9" t="n">
-        <v>112</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2586.917132596945</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.528182744979858</v>
-      </c>
-      <c r="J9" t="n">
-        <v>433</v>
-      </c>
-      <c r="K9" t="n">
-        <v>79</v>
-      </c>
       <c r="L9" t="n">
-        <v>511</v>
+        <v>607</v>
       </c>
       <c r="M9" t="n">
-        <v>6807.206312819167</v>
+        <v>6541.522877470642</v>
       </c>
       <c r="N9" t="n">
-        <v>4.731267929077148</v>
+        <v>4.573288917541504</v>
       </c>
       <c r="O9" t="n">
-        <v>1901</v>
+        <v>2070</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>6034</v>
+        <v>6603</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8136986594930645</v>
+        <v>0.8225890540362262</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6199737434540034</v>
+        <v>0.6297483555516339</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1206.298622268387</v>
+        <v>1201.961262105025</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5822539329528809</v>
+        <v>0.9575188159942627</v>
       </c>
       <c r="E10" t="n">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="H10" t="n">
-        <v>2572.261969765736</v>
+        <v>2422.776358144382</v>
       </c>
       <c r="I10" t="n">
-        <v>1.805310964584351</v>
+        <v>14.07556509971619</v>
       </c>
       <c r="J10" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="K10" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="L10" t="n">
-        <v>530</v>
+        <v>615</v>
       </c>
       <c r="M10" t="n">
-        <v>6772.754584774314</v>
+        <v>6536.356764771156</v>
       </c>
       <c r="N10" t="n">
-        <v>4.501752853393555</v>
+        <v>4.683087825775146</v>
       </c>
       <c r="O10" t="n">
-        <v>1890</v>
+        <v>2081</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>5921</v>
+        <v>6548</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8218895122849659</v>
+        <v>0.8161114355655728</v>
       </c>
       <c r="S10" t="n">
-        <v>0.620204462221563</v>
+        <v>0.6293384150629046</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1234.123415754745</v>
+        <v>1231.371012153772</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4637260437011719</v>
+        <v>1.10494589805603</v>
       </c>
       <c r="E11" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H11" t="n">
-        <v>2543.342223453529</v>
+        <v>2557.680707706273</v>
       </c>
       <c r="I11" t="n">
-        <v>1.58483099937439</v>
+        <v>18.67961502075195</v>
       </c>
       <c r="J11" t="n">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="K11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>504</v>
+        <v>619</v>
       </c>
       <c r="M11" t="n">
-        <v>6845.303741375956</v>
+        <v>6431.334117044168</v>
       </c>
       <c r="N11" t="n">
-        <v>5.096665859222412</v>
+        <v>4.741275072097778</v>
       </c>
       <c r="O11" t="n">
-        <v>1852</v>
+        <v>2063</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>5851</v>
+        <v>6557</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8197123951863272</v>
+        <v>0.8085356801957433</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6284544383209065</v>
+        <v>0.6023094646990943</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1254.770157958122</v>
+        <v>1185.555275428132</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5749921798706055</v>
+        <v>1.515537977218628</v>
       </c>
       <c r="E12" t="n">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="F12" t="n">
         <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H12" t="n">
-        <v>2267.450926594384</v>
+        <v>2228.210674302457</v>
       </c>
       <c r="I12" t="n">
-        <v>1.614748954772949</v>
+        <v>11.90110206604004</v>
       </c>
       <c r="J12" t="n">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="K12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L12" t="n">
-        <v>496</v>
+        <v>558</v>
       </c>
       <c r="M12" t="n">
-        <v>6804.117630807519</v>
+        <v>6400.01163375646</v>
       </c>
       <c r="N12" t="n">
-        <v>7.384757041931152</v>
+        <v>4.544145107269287</v>
       </c>
       <c r="O12" t="n">
-        <v>1835</v>
+        <v>2016</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5893</v>
+        <v>6427</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8155866453165355</v>
+        <v>0.8147573249437556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6667531266173479</v>
+        <v>0.6518427150116572</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1219.69848578893</v>
+        <v>1293.787655157969</v>
       </c>
       <c r="D13" t="n">
-        <v>0.548710823059082</v>
+        <v>1.418087244033813</v>
       </c>
       <c r="E13" t="n">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H13" t="n">
-        <v>2612.952808648217</v>
+        <v>2472.141940018209</v>
       </c>
       <c r="I13" t="n">
-        <v>1.688388824462891</v>
+        <v>14.35286498069763</v>
       </c>
       <c r="J13" t="n">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="K13" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="L13" t="n">
-        <v>532</v>
+        <v>595</v>
       </c>
       <c r="M13" t="n">
-        <v>6715.276710049093</v>
+        <v>6604.472289701125</v>
       </c>
       <c r="N13" t="n">
-        <v>5.216383934020996</v>
+        <v>4.753698825836182</v>
       </c>
       <c r="O13" t="n">
-        <v>1912</v>
+        <v>2104</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>6126</v>
+        <v>6743</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8183695864738219</v>
+        <v>0.8041043101694175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6108942458412686</v>
+        <v>0.6256866814517164</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1256.466277238224</v>
+        <v>1307.078965396938</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4844229221343994</v>
+        <v>1.583468675613403</v>
       </c>
       <c r="E14" t="n">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F14" t="n">
         <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="H14" t="n">
-        <v>2549.102630274429</v>
+        <v>2351.270163056413</v>
       </c>
       <c r="I14" t="n">
-        <v>1.506661176681519</v>
+        <v>12.89676403999329</v>
       </c>
       <c r="J14" t="n">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="K14" t="n">
         <v>77</v>
       </c>
       <c r="L14" t="n">
-        <v>508</v>
+        <v>561</v>
       </c>
       <c r="M14" t="n">
-        <v>6763.129768772653</v>
+        <v>6643.802047031687</v>
       </c>
       <c r="N14" t="n">
-        <v>5.231096982955933</v>
+        <v>4.649166107177734</v>
       </c>
       <c r="O14" t="n">
-        <v>1859</v>
+        <v>2062</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>5854</v>
+        <v>6457</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8142182214158161</v>
+        <v>0.8032634090925521</v>
       </c>
       <c r="S14" t="n">
-        <v>0.623088315997664</v>
+        <v>0.6460956924345884</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1265.284886518056</v>
+        <v>1240.17889649622</v>
       </c>
       <c r="D15" t="n">
-        <v>0.451930046081543</v>
+        <v>1.332836151123047</v>
       </c>
       <c r="E15" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H15" t="n">
-        <v>2369.974322896257</v>
+        <v>2330.247485343005</v>
       </c>
       <c r="I15" t="n">
-        <v>1.569034337997437</v>
+        <v>11.01040601730347</v>
       </c>
       <c r="J15" t="n">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="K15" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="L15" t="n">
-        <v>509</v>
+        <v>578</v>
       </c>
       <c r="M15" t="n">
-        <v>6730.86540398656</v>
+        <v>6605.882812320245</v>
       </c>
       <c r="N15" t="n">
-        <v>4.537945985794067</v>
+        <v>4.709511995315552</v>
       </c>
       <c r="O15" t="n">
-        <v>1858</v>
+        <v>2083</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>5915</v>
+        <v>6630</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8120175028654335</v>
+        <v>0.8122614445743367</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6478945602607701</v>
+        <v>0.647246620694361</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1297.913821409256</v>
+        <v>1214.978678859873</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6245431900024414</v>
+        <v>1.204095125198364</v>
       </c>
       <c r="E16" t="n">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H16" t="n">
-        <v>2387.430492492308</v>
+        <v>2550.831323842608</v>
       </c>
       <c r="I16" t="n">
-        <v>2.10469126701355</v>
+        <v>13.23248314857483</v>
       </c>
       <c r="J16" t="n">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="K16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L16" t="n">
-        <v>518</v>
+        <v>645</v>
       </c>
       <c r="M16" t="n">
-        <v>6791.707662334273</v>
+        <v>6543.206262560689</v>
       </c>
       <c r="N16" t="n">
-        <v>4.675241947174072</v>
+        <v>5.005892038345337</v>
       </c>
       <c r="O16" t="n">
-        <v>1881</v>
+        <v>2116</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5952</v>
+        <v>6607</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8088972779839628</v>
+        <v>0.8143144767097117</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6484786137464932</v>
+        <v>0.6101557521672352</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1201.41213795287</v>
+        <v>1279.009160552933</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4871320724487305</v>
+        <v>0.9626090526580811</v>
       </c>
       <c r="E17" t="n">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H17" t="n">
-        <v>2383.135020619256</v>
+        <v>2400.293872980371</v>
       </c>
       <c r="I17" t="n">
-        <v>1.483409881591797</v>
+        <v>12.61846137046814</v>
       </c>
       <c r="J17" t="n">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="L17" t="n">
-        <v>493</v>
+        <v>593</v>
       </c>
       <c r="M17" t="n">
-        <v>6773.418457701027</v>
+        <v>6443.388824336875</v>
       </c>
       <c r="N17" t="n">
-        <v>5.161089181900024</v>
+        <v>5.293577909469604</v>
       </c>
       <c r="O17" t="n">
-        <v>1847</v>
+        <v>2108</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>5807</v>
+        <v>6697</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8226283898661352</v>
+        <v>0.8015005464636751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6481636214414371</v>
+        <v>0.6274795859106953</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1347.115091142415</v>
+        <v>1201.35466177876</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4466891288757324</v>
+        <v>1.153323650360107</v>
       </c>
       <c r="E18" t="n">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H18" t="n">
-        <v>2468.845650660055</v>
+        <v>2295.416602393513</v>
       </c>
       <c r="I18" t="n">
-        <v>1.627801895141602</v>
+        <v>12.05465793609619</v>
       </c>
       <c r="J18" t="n">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="K18" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L18" t="n">
-        <v>512</v>
+        <v>563</v>
       </c>
       <c r="M18" t="n">
-        <v>6883.60334643902</v>
+        <v>6568.563021730003</v>
       </c>
       <c r="N18" t="n">
-        <v>4.835461139678955</v>
+        <v>5.415570974349976</v>
       </c>
       <c r="O18" t="n">
-        <v>1886</v>
+        <v>2154</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>5993</v>
+        <v>6900</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8043008838039315</v>
+        <v>0.8171054067983424</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6413439987158438</v>
+        <v>0.6505450895728857</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1247.414306024057</v>
+        <v>1148.50954947059</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4884040355682373</v>
+        <v>1.125110149383545</v>
       </c>
       <c r="E19" t="n">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H19" t="n">
-        <v>2380.34156149025</v>
+        <v>2427.256736294667</v>
       </c>
       <c r="I19" t="n">
-        <v>1.714040994644165</v>
+        <v>12.22074294090271</v>
       </c>
       <c r="J19" t="n">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="K19" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L19" t="n">
-        <v>517</v>
+        <v>590</v>
       </c>
       <c r="M19" t="n">
-        <v>6750.069870749466</v>
+        <v>6666.250825788778</v>
       </c>
       <c r="N19" t="n">
-        <v>4.568099975585938</v>
+        <v>5.114950180053711</v>
       </c>
       <c r="O19" t="n">
-        <v>1840</v>
+        <v>2115</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>5888</v>
+        <v>6747</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8151997934970182</v>
+        <v>0.827712820971645</v>
       </c>
       <c r="S19" t="n">
-        <v>0.647360455955405</v>
+        <v>0.6358887777062507</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1274.550794704371</v>
+        <v>1335.065195523871</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5340380668640137</v>
+        <v>1.188057899475098</v>
       </c>
       <c r="E20" t="n">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="F20" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H20" t="n">
-        <v>2613.933304314208</v>
+        <v>2444.878875100004</v>
       </c>
       <c r="I20" t="n">
-        <v>2.056779861450195</v>
+        <v>14.31250882148743</v>
       </c>
       <c r="J20" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="K20" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="L20" t="n">
-        <v>540</v>
+        <v>626</v>
       </c>
       <c r="M20" t="n">
-        <v>6767.060549150746</v>
+        <v>6540.773526309712</v>
       </c>
       <c r="N20" t="n">
-        <v>4.73459005355835</v>
+        <v>5.700908899307251</v>
       </c>
       <c r="O20" t="n">
-        <v>1900</v>
+        <v>2086</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>6040</v>
+        <v>6665</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8116537031925443</v>
+        <v>0.795885732757191</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6137269224460756</v>
+        <v>0.6262095201331028</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1225.545737798025</v>
+        <v>1259.586381411077</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5593807697296143</v>
+        <v>1.451653003692627</v>
       </c>
       <c r="E21" t="n">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="F21" t="n">
         <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H21" t="n">
-        <v>2432.150590750401</v>
+        <v>2450.06136054491</v>
       </c>
       <c r="I21" t="n">
-        <v>1.441407203674316</v>
+        <v>14.3394832611084</v>
       </c>
       <c r="J21" t="n">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="K21" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L21" t="n">
-        <v>495</v>
+        <v>582</v>
       </c>
       <c r="M21" t="n">
-        <v>6690.800410542064</v>
+        <v>6510.700458565973</v>
       </c>
       <c r="N21" t="n">
-        <v>5.065921068191528</v>
+        <v>4.986258268356323</v>
       </c>
       <c r="O21" t="n">
-        <v>1858</v>
+        <v>2099</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>5941</v>
+        <v>6768</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8168312215879211</v>
+        <v>0.8065359649968431</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6364933279255661</v>
+        <v>0.6236869786688739</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1244.809844891214</v>
+        <v>1121.559553020345</v>
       </c>
       <c r="D22" t="n">
-        <v>0.428358793258667</v>
+        <v>1.235038280487061</v>
       </c>
       <c r="E22" t="n">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="F22" t="n">
+        <v>55</v>
+      </c>
+      <c r="G22" t="n">
+        <v>116</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2376.629293167236</v>
+      </c>
+      <c r="I22" t="n">
+        <v>12.3796763420105</v>
+      </c>
+      <c r="J22" t="n">
+        <v>439</v>
+      </c>
+      <c r="K22" t="n">
         <v>70</v>
       </c>
-      <c r="G22" t="n">
-        <v>95</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2487.463079042809</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.499128103256226</v>
-      </c>
-      <c r="J22" t="n">
-        <v>434</v>
-      </c>
-      <c r="K22" t="n">
-        <v>65</v>
-      </c>
       <c r="L22" t="n">
-        <v>498</v>
+        <v>593</v>
       </c>
       <c r="M22" t="n">
-        <v>6750.269933529787</v>
+        <v>6520.933209175438</v>
       </c>
       <c r="N22" t="n">
-        <v>5.028214693069458</v>
+        <v>4.941298961639404</v>
       </c>
       <c r="O22" t="n">
-        <v>1890</v>
+        <v>2077</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>6042</v>
+        <v>6667</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8155911012227788</v>
+        <v>0.8280062811497244</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6315016875566503</v>
+        <v>0.6355384701957779</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1190.949361805743</v>
+        <v>1327.183516935904</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4502429962158203</v>
+        <v>0.8231229782104492</v>
       </c>
       <c r="E23" t="n">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="F23" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H23" t="n">
-        <v>2456.720509038555</v>
+        <v>2416.209416173979</v>
       </c>
       <c r="I23" t="n">
-        <v>1.862799167633057</v>
+        <v>14.13871932029724</v>
       </c>
       <c r="J23" t="n">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="K23" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L23" t="n">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="M23" t="n">
-        <v>6807.325470717583</v>
+        <v>6528.804646710292</v>
       </c>
       <c r="N23" t="n">
-        <v>6.723730802536011</v>
+        <v>4.865993976593018</v>
       </c>
       <c r="O23" t="n">
-        <v>1873</v>
+        <v>2082</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>5987</v>
+        <v>6691</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8250488584791875</v>
+        <v>0.7967187580647493</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6391063539408548</v>
+        <v>0.6299154980243667</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1214.117201398808</v>
+        <v>1282.989647565322</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7436039447784424</v>
+        <v>1.071010112762451</v>
       </c>
       <c r="E24" t="n">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H24" t="n">
-        <v>2539.66555742239</v>
+        <v>2494.422653426203</v>
       </c>
       <c r="I24" t="n">
-        <v>2.303559064865112</v>
+        <v>16.59580278396606</v>
       </c>
       <c r="J24" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K24" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L24" t="n">
-        <v>522</v>
+        <v>617</v>
       </c>
       <c r="M24" t="n">
-        <v>6801.849091449336</v>
+        <v>6462.923746485613</v>
       </c>
       <c r="N24" t="n">
-        <v>5.622860908508301</v>
+        <v>4.831544160842896</v>
       </c>
       <c r="O24" t="n">
-        <v>1874</v>
+        <v>2117</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>6037</v>
+        <v>6688</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8215018908718387</v>
+        <v>0.8014846379298562</v>
       </c>
       <c r="S24" t="n">
-        <v>0.626621302049317</v>
+        <v>0.6140411443377137</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1249.13652360479</v>
+        <v>1228.512034385563</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5545830726623535</v>
+        <v>1.808586120605469</v>
       </c>
       <c r="E25" t="n">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="F25" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G25" t="n">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="H25" t="n">
-        <v>2460.845748294177</v>
+        <v>2506.493294758544</v>
       </c>
       <c r="I25" t="n">
-        <v>1.634554862976074</v>
+        <v>13.57841372489929</v>
       </c>
       <c r="J25" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="L25" t="n">
-        <v>544</v>
+        <v>633</v>
       </c>
       <c r="M25" t="n">
-        <v>6777.167561094828</v>
+        <v>6669.587923663202</v>
       </c>
       <c r="N25" t="n">
-        <v>4.421442985534668</v>
+        <v>5.558242082595825</v>
       </c>
       <c r="O25" t="n">
-        <v>1887</v>
+        <v>2103</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>6042</v>
+        <v>6675</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8156845743676735</v>
+        <v>0.8158039074607754</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6368917064378091</v>
+        <v>0.6241906811265368</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1217.041826624746</v>
+        <v>1273.608949963498</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4490890502929688</v>
+        <v>1.347157955169678</v>
       </c>
       <c r="E26" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F26" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G26" t="n">
         <v>120</v>
       </c>
       <c r="H26" t="n">
-        <v>2344.693494523951</v>
+        <v>2362.055351023979</v>
       </c>
       <c r="I26" t="n">
-        <v>1.384383916854858</v>
+        <v>14.58054399490356</v>
       </c>
       <c r="J26" t="n">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="K26" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L26" t="n">
-        <v>470</v>
+        <v>576</v>
       </c>
       <c r="M26" t="n">
-        <v>6632.613070050503</v>
+        <v>6598.200030644444</v>
       </c>
       <c r="N26" t="n">
-        <v>4.624993801116943</v>
+        <v>5.056851863861084</v>
       </c>
       <c r="O26" t="n">
-        <v>1821</v>
+        <v>2093</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>5743</v>
+        <v>6610</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8165064336226266</v>
+        <v>0.8069763050455587</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6464902339755969</v>
+        <v>0.6420151950450527</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1203.306452587495</v>
+        <v>1367.221308980318</v>
       </c>
       <c r="D27" t="n">
-        <v>0.482903003692627</v>
+        <v>1.177689790725708</v>
       </c>
       <c r="E27" t="n">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G27" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="H27" t="n">
-        <v>2332.018171788482</v>
+        <v>2432.449639189423</v>
       </c>
       <c r="I27" t="n">
-        <v>1.639808177947998</v>
+        <v>13.21680116653442</v>
       </c>
       <c r="J27" t="n">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="K27" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L27" t="n">
-        <v>515</v>
+        <v>593</v>
       </c>
       <c r="M27" t="n">
-        <v>6788.658919693749</v>
+        <v>6675.110167721731</v>
       </c>
       <c r="N27" t="n">
-        <v>6.43566370010376</v>
+        <v>5.04265284538269</v>
       </c>
       <c r="O27" t="n">
-        <v>1888</v>
+        <v>2052</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>6035</v>
+        <v>6497</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8227475460437806</v>
+        <v>0.7951762181257059</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6564832319055904</v>
+        <v>0.635594083382801</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1297.669115083912</v>
+        <v>1266.08492249582</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5831599235534668</v>
+        <v>1.200587034225464</v>
       </c>
       <c r="E28" t="n">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="F28" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G28" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H28" t="n">
-        <v>2427.516244157046</v>
+        <v>2507.007865184046</v>
       </c>
       <c r="I28" t="n">
-        <v>1.547993659973145</v>
+        <v>13.71814203262329</v>
       </c>
       <c r="J28" t="n">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="K28" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="L28" t="n">
-        <v>506</v>
+        <v>614</v>
       </c>
       <c r="M28" t="n">
-        <v>6741.706281069077</v>
+        <v>6594.392284738418</v>
       </c>
       <c r="N28" t="n">
-        <v>6.716570138931274</v>
+        <v>4.310683012008667</v>
       </c>
       <c r="O28" t="n">
-        <v>1840</v>
+        <v>2134</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5898</v>
+        <v>6838</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8075162190426765</v>
+        <v>0.8080058225492659</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6399255406641507</v>
+        <v>0.6198273082743223</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1152.137426283655</v>
+        <v>1235.029413747405</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4776370525360107</v>
+        <v>1.062405824661255</v>
       </c>
       <c r="E29" t="n">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F29" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H29" t="n">
-        <v>2439.155879889439</v>
+        <v>2461.346555357723</v>
       </c>
       <c r="I29" t="n">
-        <v>1.393353223800659</v>
+        <v>12.70480704307556</v>
       </c>
       <c r="J29" t="n">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="K29" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L29" t="n">
-        <v>484</v>
+        <v>611</v>
       </c>
       <c r="M29" t="n">
-        <v>6626.334751745724</v>
+        <v>6476.466842761499</v>
       </c>
       <c r="N29" t="n">
-        <v>6.605361223220825</v>
+        <v>4.270076990127563</v>
       </c>
       <c r="O29" t="n">
-        <v>1841</v>
+        <v>2098</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>5892</v>
+        <v>6620</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8261274943919606</v>
+        <v>0.8093050665228447</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6318996894554962</v>
+        <v>0.6199553529547245</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1198.408093265732</v>
+        <v>1235.043947586359</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7675967216491699</v>
+        <v>1.006536245346069</v>
       </c>
       <c r="E30" t="n">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G30" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="H30" t="n">
-        <v>2561.654389258424</v>
+        <v>2452.436334904504</v>
       </c>
       <c r="I30" t="n">
-        <v>1.99298095703125</v>
+        <v>12.80897903442383</v>
       </c>
       <c r="J30" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="K30" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="L30" t="n">
-        <v>498</v>
+        <v>616</v>
       </c>
       <c r="M30" t="n">
-        <v>6721.518751332102</v>
+        <v>6535.997205104888</v>
       </c>
       <c r="N30" t="n">
-        <v>8.260468006134033</v>
+        <v>4.904283761978149</v>
       </c>
       <c r="O30" t="n">
-        <v>1844</v>
+        <v>2076</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>5956</v>
+        <v>6571</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8217057576417195</v>
+        <v>0.8110397068986294</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6188875633575012</v>
+        <v>0.6247800820678062</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1256.746385030064</v>
+        <v>1240.940597230517</v>
       </c>
       <c r="D31" t="n">
-        <v>0.534843921661377</v>
+        <v>1.015632152557373</v>
       </c>
       <c r="E31" t="n">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G31" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="H31" t="n">
-        <v>2486.885290385813</v>
+        <v>2619.226306741526</v>
       </c>
       <c r="I31" t="n">
-        <v>1.940433025360107</v>
+        <v>16.2241837978363</v>
       </c>
       <c r="J31" t="n">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="K31" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L31" t="n">
-        <v>524</v>
+        <v>653</v>
       </c>
       <c r="M31" t="n">
-        <v>6743.821794455842</v>
+        <v>6565.271526758307</v>
       </c>
       <c r="N31" t="n">
-        <v>5.566504001617432</v>
+        <v>4.566097974777222</v>
       </c>
       <c r="O31" t="n">
-        <v>1869</v>
+        <v>2122</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>5991</v>
+        <v>6698</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8136447813518373</v>
+        <v>0.8109841166244576</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6312350227833267</v>
+        <v>0.6010482893104644</v>
       </c>
     </row>
   </sheetData>
